--- a/artfynd/A 30840-2023 artfynd.xlsx
+++ b/artfynd/A 30840-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30840-2023 artfynd.xlsx
+++ b/artfynd/A 30840-2023 artfynd.xlsx
@@ -7912,12 +7912,7 @@
         <v>117060293</v>
       </c>
       <c r="B63" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7950,7 +7945,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ön Haverö (Ön Haverö), Mpd</t>
+          <t>Ön Haverö, Ön Haverö, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">

--- a/artfynd/A 30840-2023 artfynd.xlsx
+++ b/artfynd/A 30840-2023 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>117060293</v>
       </c>
       <c r="B63" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30840-2023 artfynd.xlsx
+++ b/artfynd/A 30840-2023 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>117060293</v>
       </c>
       <c r="B63" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30840-2023 artfynd.xlsx
+++ b/artfynd/A 30840-2023 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>117060293</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30840-2023 artfynd.xlsx
+++ b/artfynd/A 30840-2023 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>117060293</v>
       </c>
       <c r="B63" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30840-2023 artfynd.xlsx
+++ b/artfynd/A 30840-2023 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>117060293</v>
       </c>
       <c r="B63" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 30840-2023 artfynd.xlsx
+++ b/artfynd/A 30840-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112721960</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111052885</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112721998</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112722428</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78248288</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111051932</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111052497</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742670</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117060293</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112722275</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1855,6 +1910,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742633</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1963,6 +2023,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112722288</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2061,6 +2126,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742694</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117060588</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2288,6 +2363,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111052144</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111052223</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2504,6 +2589,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111052279</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2621,6 +2711,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111052330</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2729,6 +2824,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111052639</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2835,6 +2935,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111266302</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2941,6 +3046,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111266512</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3047,6 +3157,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378856</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3153,6 +3268,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378866</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3259,6 +3379,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378874</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3365,6 +3490,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378884</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3471,6 +3601,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378893</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3577,6 +3712,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378913</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3683,6 +3823,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378933</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3789,6 +3934,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378946</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3895,6 +4045,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378954</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4001,6 +4156,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111378964</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4118,6 +4278,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112722140</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4235,6 +4400,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112722228</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4352,6 +4522,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112722971</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4469,6 +4644,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112722994</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4586,6 +4766,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723052</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4703,6 +4888,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723099</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4819,6 +5009,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117056696</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4935,6 +5130,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117056724</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5051,6 +5251,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117056806</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5167,6 +5372,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057017</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5283,6 +5493,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057081</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5399,6 +5614,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057120</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5515,6 +5735,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057151</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5631,6 +5856,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057363</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5747,6 +5977,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057428</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5863,6 +6098,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057471</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5979,6 +6219,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057525</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6095,6 +6340,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057577</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6211,6 +6461,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057616</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6327,6 +6582,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057684</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6443,6 +6703,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057719</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6559,6 +6824,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057754</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6675,6 +6945,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057779</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6791,6 +7066,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057819</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6907,6 +7187,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117058009</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7023,6 +7308,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117058266</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7139,6 +7429,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117058422</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7255,6 +7550,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117058495</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7371,6 +7671,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117058604</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7487,6 +7792,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117058835</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7603,6 +7913,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117059474</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7719,6 +8034,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117059556</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7835,6 +8155,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117059679</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7951,6 +8276,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117060979</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8067,6 +8397,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117061008</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8173,6 +8508,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120549497</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8281,6 +8621,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111052010</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8388,8 +8733,84 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117057211</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>